--- a/data/Jharkhand/Ranchi/Ranchi_Schools.xlsx
+++ b/data/Jharkhand/Ranchi/Ranchi_Schools.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,6 +570,446 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>St. Michael's School</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>stmichaelsranchi@gmail.com</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Jajpur, Soparom, Itki Road, Ranchi</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>96932-10060</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>St. Thomas School</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>stthomasschoolranchi@gmail.com</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>HEC Colony, Dhurwa, Ranchi</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0651 2446649</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Bridgeford School</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>info@bridgefordschool.com</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Tupudana, Ranchi</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>89868 07523</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Tender Heart Senior Secondary School</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>thsss.ranchi@gmail.com</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Tupudana, Ranchi</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>9204060667</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sapphire International School</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>info@sisranchi.com</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Hardag, Ranchi</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>840 600 0211</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Manan Vidya</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>mananvidya@gmail.com</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Dumardaga, Ranchi</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0651-2273600</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Taurian World School</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>admissions@tws.edu.in</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Knowledge City, Hazam, Ranchi</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>93089 91112</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sarala Birla Public School</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>info@sbpsranchi.com</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Birla Knowledge City, Ranchi</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>9507035717</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>St. Francis School</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>sfs_harmu@hotmail.com</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Harmu, Ranchi</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>8987705291</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Army Public School</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>asr8208@gmail.com</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Dipatoli Cantt, Ranchi</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0651-2273354</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>GD Goenka Public School</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>gdgoenkaranchi@gmail.com</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ranchi</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>95504 79500</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Firayalal Public School</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>info@firayalalpublicschool.com</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Main Road, Ranchi</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>9264431217</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Guru Nanak Higher Secondary School</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>gnhssran@gmail.com</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Guru Nanak Pura, Ranchi</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>983 514 3657</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Loreto Convent</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>contact.loretoranchi@gmail.com</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Doranda, Ranchi</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>0651-2410042</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>St. Anthony's School</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>stanthonys1971@gmail.com</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Doranda, Ranchi</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>9204060251</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Vikas Vidyalaya</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>principalvvranchi@gmail.com</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Neori Vikas, Ranchi</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>6201999015</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>St. Charles School</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>stcharleshatia@yahoo.in</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Hatia, Ranchi</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>7209350801</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Montfort School</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>montranchi@gmail.com</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Hathiagonda, Ranchi</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>9934165815</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Sacred Heart School</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>sacredheartranchi@rediffmail.com</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Hulhundu, Ranchi</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>8789732436</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Bishop's School</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>bishopschoolbahubazar@yahoo.com</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Old H.B. Road, Ranchi</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>0651-2350344</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
